--- a/COMPRAS--.xlsx
+++ b/COMPRAS--.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlopez\Desktop\Jazmín\COMPRAS 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E69473-3B62-4FBA-96F7-EACFA0B1CC06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C5F5CA-F5F7-411C-9FA4-284C7471A534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{B308AD57-4154-456E-A659-7D1101AC72C4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{B308AD57-4154-456E-A659-7D1101AC72C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Insumos-materia prima-reventa" sheetId="5" r:id="rId1"/>
@@ -19,9 +19,10 @@
     <sheet name="Historial - Servicios" sheetId="7" r:id="rId4"/>
     <sheet name="Cotizaciones" sheetId="4" r:id="rId5"/>
     <sheet name="TC_BNA xlsx" sheetId="3" r:id="rId6"/>
+    <sheet name="PROVEEDORES" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="DatosExternos_1" localSheetId="5" hidden="1">'TC_BNA xlsx'!$A$1:$C$66</definedName>
+    <definedName name="DatosExternos_1" localSheetId="5" hidden="1">'TC_BNA xlsx'!$A$1:$C$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2752" uniqueCount="532">
   <si>
     <t>Fecha</t>
   </si>
@@ -1401,6 +1402,299 @@
   </si>
   <si>
     <t>Subtotal USD</t>
+  </si>
+  <si>
+    <t>Total Proveedores</t>
+  </si>
+  <si>
+    <t>Rubro / Categoría</t>
+  </si>
+  <si>
+    <t>Insumo</t>
+  </si>
+  <si>
+    <t>Contacto</t>
+  </si>
+  <si>
+    <t>Dirección</t>
+  </si>
+  <si>
+    <t>Métodos de pago</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Habitual</t>
+  </si>
+  <si>
+    <t>Alternativo</t>
+  </si>
+  <si>
+    <t>Agostina +54 9 11 3051-4727</t>
+  </si>
+  <si>
+    <t>Gustavo +54 9 11 5810-2483</t>
+  </si>
+  <si>
+    <t>República del Líbano 4144 - Villa Lynch</t>
+  </si>
+  <si>
+    <t>E-cheq 30 días ff / 
+Transferencia</t>
+  </si>
+  <si>
+    <t>Av. 9 de Julio 816, B1833BRV Turdera, 
+Provincia de Buenos Aires</t>
+  </si>
+  <si>
+    <t>Contado 7 días</t>
+  </si>
+  <si>
+    <t>Bolsas tubo 100mic / 80 mic</t>
+  </si>
+  <si>
+    <t>Daniel +54 9 11 3339-4363</t>
+  </si>
+  <si>
+    <t>General savio 26, Garin, Bs.As.</t>
+  </si>
+  <si>
+    <t>E-cheq /Transf. 
+Contra Entrega 7 días</t>
+  </si>
+  <si>
+    <t>Mónica +54 9 11 2785-9442</t>
+  </si>
+  <si>
+    <t>Matheu ( Calle Nro. 56 ) 1156   
+Villa Maipú    San Martín   Argentina</t>
+  </si>
+  <si>
+    <t>Contra Entrega</t>
+  </si>
+  <si>
+    <t>Buena calidad del producto, 
+buena gestión con el proveedor.</t>
+  </si>
+  <si>
+    <t>Aún se está evaluando calidad del producto. Mejor precio que el habitual.</t>
+  </si>
+  <si>
+    <t>Precio elevado, sin problemas con la
+calidad del producto.</t>
+  </si>
+  <si>
+    <t>Stretch 10cm cristal/negro/rojo, stretch 50cm c/mango, cartón corrugado, rollo pluribol</t>
+  </si>
+  <si>
+    <t>Stretch 10cm cristal/negro, stretch 50cm c/mango, plancha de cartón, rollo pluribol</t>
+  </si>
+  <si>
+    <t>Zuncho verde, Stretch 10cm cristal/negro, stretch 50 cm c/mango</t>
+  </si>
+  <si>
+    <t>Lucía +54 9 11 3484-6437</t>
+  </si>
+  <si>
+    <t>Austria 100, B1812 Cañuelas, 
+Provincia de Buenos Aires</t>
+  </si>
+  <si>
+    <t>E-cheq 30 días ff</t>
+  </si>
+  <si>
+    <t>Les compramos únicamente el zuncho.</t>
+  </si>
+  <si>
+    <t>Abrazaderas Damat</t>
+  </si>
+  <si>
+    <t>Aumento del 4% notificado por el proveedor</t>
+  </si>
+  <si>
+    <t>Miguel +54 9 11 2652-0570</t>
+  </si>
+  <si>
+    <t>MOM 2945 - Nueva Pompeya - CABA</t>
+  </si>
+  <si>
+    <t>Precintos 500x7,6; 450x7,6; 250x4,6</t>
+  </si>
+  <si>
+    <t>Telgopor  450x50x50; 600x50x50</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +54 9 11 5420-0917</t>
+  </si>
+  <si>
+    <t>Camino de la tradición 1066 / 1056 - 
+Luis Guillon</t>
+  </si>
+  <si>
+    <t>Transf. 7 días ff</t>
+  </si>
+  <si>
+    <t>Pallets arlog 1200x1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +54 9 11 3500-7414</t>
+  </si>
+  <si>
+    <t>Parque Logístico 9 de Abril - Deposito 17</t>
+  </si>
+  <si>
+    <t>Bolsas arpilleras 60x100</t>
+  </si>
+  <si>
+    <t>Damario</t>
+  </si>
+  <si>
+    <t>Franco +54 9 2224 55-3744</t>
+  </si>
+  <si>
+    <t>Miguel Martínez 1637 - Alejandro Korn, 
+Buenos Aires</t>
+  </si>
+  <si>
+    <t>Transf./E-cheq 
+15 días FF</t>
+  </si>
+  <si>
+    <t>Etiquetas lunares, flejes, impresoras</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +54 9 11 3349-9607</t>
+  </si>
+  <si>
+    <t>Belgrano 211 E/Garcia y Rawson - Panamericana Km 56.5 - 
+Pilar (Buenos Aires)</t>
+  </si>
+  <si>
+    <t>Insumos de soldadura</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +54 9 11 4448-2246</t>
+  </si>
+  <si>
+    <t>Av. Hipólito Yrigoyen 15165 (1852) - 
+Burzaco - Buenos Aires</t>
+  </si>
+  <si>
+    <t>Transf. Contra 
+Entrega</t>
+  </si>
+  <si>
+    <t>Discos de corte, flapp, desbaste, sensitiva</t>
+  </si>
+  <si>
+    <t>Gisela +54 9 11 6898-8738</t>
+  </si>
+  <si>
+    <t>Parque Industrial Cañuelas I
+CP1814 - Cañuelas - Buenos Aires.</t>
+  </si>
+  <si>
+    <t>Cintas métricas</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +54 9 11 7886-9830</t>
+  </si>
+  <si>
+    <t>Av. La Plata 3761 - (B1879) Quilmes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +54 9 11 4940-6593</t>
+  </si>
+  <si>
+    <t>Calle 1236 n° 629 , lote 5 y 6 (PITEC) - 
+Ingeniero Allan (1891) - Pcia de Buenos Aires - Argentina</t>
+  </si>
+  <si>
+    <t>Cheques posdatados
+30 días ff</t>
+  </si>
+  <si>
+    <t>Pinturería
+Giannoni</t>
+  </si>
+  <si>
+    <t>Artículos de ferretería</t>
+  </si>
+  <si>
+    <t>Marcelo +54 9 11 5563-9300</t>
+  </si>
+  <si>
+    <t>H. Yrigoyen 13411 - Adrogué</t>
+  </si>
+  <si>
+    <t>Cuenta Corriente</t>
+  </si>
+  <si>
+    <t>Aerosoles / latas de pintura</t>
+  </si>
+  <si>
+    <t>Juan +54 9 11 3039-9555</t>
+  </si>
+  <si>
+    <t>Av. H. Yrigoyen 11.144 - Turdera -
+Buenos Aires</t>
+  </si>
+  <si>
+    <t>Transf. 48hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpamet </t>
+  </si>
+  <si>
+    <t>Hoja de sierra / Afilado de sierras</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> +54 9 11 6567-3640</t>
+  </si>
+  <si>
+    <t>Av. San Martín 3007, B1824 Lanús, 
+Provincia de Buenos Aires</t>
+  </si>
+  <si>
+    <t>Transf. 30 días ff</t>
+  </si>
+  <si>
+    <t>EPP (Guantes, lentes seg, fajas, 
+indumentaria de trabajo)</t>
+  </si>
+  <si>
+    <t>General Fernández de la Cruz 80. Ituzaingó</t>
+  </si>
+  <si>
+    <t>Barbi +54 9 11 4475-5444</t>
+  </si>
+  <si>
+    <t>Guantes, cascos, elem. De cascos</t>
+  </si>
+  <si>
+    <t>Gustavo B. +54 9 11 6470-7707</t>
+  </si>
+  <si>
+    <t>Chapas</t>
+  </si>
+  <si>
+    <t>Barbijos</t>
+  </si>
+  <si>
+    <t>Medicamentos</t>
+  </si>
+  <si>
+    <t>Farmacia Rapetti</t>
+  </si>
+  <si>
+    <t>caja</t>
+  </si>
+  <si>
+    <t>Varios</t>
+  </si>
+  <si>
+    <t>No entiendo por qué el iva lo cobró 8mil..(por eso lo cargue como otro prod)</t>
   </si>
 </sst>
 </file>
@@ -1412,7 +1706,7 @@
     <numFmt numFmtId="164" formatCode="[$USD]\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="_-[$USD]\ * #,##0.00_-;\-[$USD]\ * #,##0.00_-;_-[$USD]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1442,6 +1736,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1457,12 +1757,69 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1474,7 +1831,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1626,6 +1983,72 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2158,8 +2581,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0964451C-E151-40C8-8323-150CDBA21896}" name="Tabla1" displayName="Tabla1" ref="B1:E277" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
-  <autoFilter ref="B1:E277" xr:uid="{0964451C-E151-40C8-8323-150CDBA21896}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0964451C-E151-40C8-8323-150CDBA21896}" name="Tabla1" displayName="Tabla1" ref="B1:E280" totalsRowShown="0" headerRowDxfId="75" dataDxfId="74">
+  <autoFilter ref="B1:E280" xr:uid="{0964451C-E151-40C8-8323-150CDBA21896}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{AB5D9A33-E191-41C6-93B0-54C2C44F2DFF}" name="Rubro" dataDxfId="73"/>
     <tableColumn id="4" xr3:uid="{12812716-6B50-479D-925E-9721C7EB89A6}" name="Artículos" dataDxfId="72"/>
@@ -2171,8 +2594,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F1B462DC-E411-49FF-AB3A-EC7276A9A36C}" name="Tabla5" displayName="Tabla5" ref="G1:H11" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
-  <autoFilter ref="G1:H11" xr:uid="{F1B462DC-E411-49FF-AB3A-EC7276A9A36C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F1B462DC-E411-49FF-AB3A-EC7276A9A36C}" name="Tabla5" displayName="Tabla5" ref="G1:H12" totalsRowShown="0" headerRowDxfId="69" dataDxfId="68">
+  <autoFilter ref="G1:H12" xr:uid="{F1B462DC-E411-49FF-AB3A-EC7276A9A36C}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{39DE0900-4579-4ADC-BB27-EB6F94B5F0E7}" name="Moneda" dataDxfId="67"/>
     <tableColumn id="2" xr3:uid="{EEB7978B-7B61-4FEF-A09A-06FF924B019B}" name="Unidad" dataDxfId="66"/>
@@ -2182,8 +2605,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{115DD642-7658-4C68-8CBF-859AD140DAB8}" name="Tabla7" displayName="Tabla7" ref="B1:E57" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
-  <autoFilter ref="B1:E57" xr:uid="{115DD642-7658-4C68-8CBF-859AD140DAB8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{115DD642-7658-4C68-8CBF-859AD140DAB8}" name="Tabla7" displayName="Tabla7" ref="B1:E58" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
+  <autoFilter ref="B1:E58" xr:uid="{115DD642-7658-4C68-8CBF-859AD140DAB8}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{7E2D192C-45B7-4464-A453-46829B7F415E}" name="Rubro" dataDxfId="63"/>
     <tableColumn id="2" xr3:uid="{B8301FE9-4492-4C7D-BFAA-19AC92D1C606}" name="Artículos" dataDxfId="62"/>
@@ -2322,8 +2745,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A23EE778-0A37-4C5B-A079-40DCB5E66B91}" name="TC_BNA_xlsx" displayName="TC_BNA_xlsx" ref="A1:C66" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C66" xr:uid="{A23EE778-0A37-4C5B-A079-40DCB5E66B91}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A23EE778-0A37-4C5B-A079-40DCB5E66B91}" name="TC_BNA_xlsx" displayName="TC_BNA_xlsx" ref="A1:C69" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:C69" xr:uid="{A23EE778-0A37-4C5B-A079-40DCB5E66B91}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E515A79D-B63A-47AB-8A48-12E5441E669E}" uniqueName="1" name="Fecha cotizacion" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{10A86502-EFF4-447F-8007-220F70C7AED7}" uniqueName="2" name="Compra" queryTableFieldId="2" dataDxfId="2"/>
@@ -2650,7 +3073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8073DF13-FAB4-46A9-AFF8-785A81099BFD}">
-  <dimension ref="B1:H277"/>
+  <dimension ref="B1:H280"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="38"/>
@@ -2847,6 +3270,10 @@
       <c r="D12" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1" t="s">
+        <v>529</v>
+      </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="38" t="s">
@@ -2922,7 +3349,7 @@
         <v>41</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>113</v>
+        <v>528</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
@@ -2933,7 +3360,7 @@
         <v>42</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>113</v>
+        <v>528</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
@@ -2944,7 +3371,7 @@
         <v>43</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>113</v>
+        <v>528</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
@@ -2955,7 +3382,7 @@
         <v>44</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>113</v>
+        <v>528</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
@@ -2966,7 +3393,7 @@
         <v>45</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>113</v>
+        <v>528</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
@@ -2977,7 +3404,7 @@
         <v>46</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>113</v>
+        <v>528</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
@@ -2988,7 +3415,7 @@
         <v>47</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>113</v>
+        <v>528</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
@@ -2999,40 +3426,40 @@
         <v>48</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>113</v>
+        <v>528</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="38" t="s">
-        <v>247</v>
+        <v>113</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>49</v>
+        <v>526</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>114</v>
+        <v>528</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="38" t="s">
-        <v>247</v>
+        <v>113</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>50</v>
+        <v>527</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>114</v>
+        <v>528</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="38" t="s">
-        <v>247</v>
+        <v>113</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>51</v>
+        <v>530</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>114</v>
+        <v>528</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
@@ -3040,7 +3467,7 @@
         <v>247</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>114</v>
@@ -3048,202 +3475,202 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="38" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="38" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="38" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="38" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>115</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="38" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>115</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="38" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>115</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="38" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B38" s="38" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="38" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B40" s="38" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B41" s="38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B42" s="38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="38" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="38" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B45" s="38" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B46" s="38" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>68</v>
+        <v>65</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="38" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>22</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="38" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>22</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="38" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
@@ -3251,7 +3678,7 @@
         <v>251</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>22</v>
@@ -3262,7 +3689,7 @@
         <v>251</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>22</v>
@@ -3273,7 +3700,7 @@
         <v>251</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>22</v>
@@ -3284,7 +3711,7 @@
         <v>251</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>22</v>
@@ -3295,7 +3722,7 @@
         <v>251</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>22</v>
@@ -3306,7 +3733,7 @@
         <v>251</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>22</v>
@@ -3317,10 +3744,10 @@
         <v>251</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
@@ -3328,10 +3755,10 @@
         <v>251</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
@@ -3339,10 +3766,10 @@
         <v>251</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
@@ -3350,7 +3777,7 @@
         <v>251</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>119</v>
@@ -3361,7 +3788,7 @@
         <v>251</v>
       </c>
       <c r="C60" s="38" t="s">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>119</v>
@@ -3372,7 +3799,7 @@
         <v>251</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>119</v>
@@ -3380,54 +3807,57 @@
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="38" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C62" s="38" t="s">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="38" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>81</v>
+        <v>209</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="38" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="C64" s="38" t="s">
-        <v>82</v>
+        <v>210</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="38" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="38" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C66" s="38" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
@@ -3435,10 +3865,7 @@
         <v>245</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
@@ -3446,7 +3873,7 @@
         <v>245</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>122</v>
@@ -3454,13 +3881,13 @@
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="38" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
@@ -3468,7 +3895,7 @@
         <v>245</v>
       </c>
       <c r="C70" s="38" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>122</v>
@@ -3479,10 +3906,10 @@
         <v>245</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
@@ -3490,10 +3917,10 @@
         <v>245</v>
       </c>
       <c r="C72" s="38" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
@@ -3501,10 +3928,10 @@
         <v>245</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
@@ -3512,7 +3939,7 @@
         <v>245</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>124</v>
@@ -3520,73 +3947,73 @@
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="38" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="38" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C76" s="38" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="38" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>95</v>
+        <v>92</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="38" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>96</v>
+        <v>93</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="38" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" s="38" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C80" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="38" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C81" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
@@ -3594,10 +4021,10 @@
         <v>245</v>
       </c>
       <c r="C82" s="38" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
@@ -3605,10 +4032,10 @@
         <v>245</v>
       </c>
       <c r="C83" s="38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
@@ -3616,10 +4043,10 @@
         <v>245</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
@@ -3627,21 +4054,21 @@
         <v>245</v>
       </c>
       <c r="C85" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="38" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C86" s="38" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
@@ -3649,10 +4076,10 @@
         <v>245</v>
       </c>
       <c r="C87" s="38" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
@@ -3660,21 +4087,21 @@
         <v>245</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="38" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C89" s="38" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
@@ -3682,10 +4109,10 @@
         <v>245</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>24</v>
+        <v>130</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
@@ -3693,10 +4120,10 @@
         <v>245</v>
       </c>
       <c r="C91" s="38" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>24</v>
+        <v>130</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
@@ -3704,10 +4131,10 @@
         <v>245</v>
       </c>
       <c r="C92" s="38" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>131</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
@@ -3715,10 +4142,10 @@
         <v>245</v>
       </c>
       <c r="C93" s="38" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
@@ -3726,10 +4153,10 @@
         <v>245</v>
       </c>
       <c r="C94" s="38" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
@@ -3737,10 +4164,10 @@
         <v>245</v>
       </c>
       <c r="C95" s="38" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
@@ -3748,43 +4175,43 @@
         <v>245</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="38" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>204</v>
+        <v>134</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>205</v>
+        <v>124</v>
       </c>
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98" s="38" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99" s="38" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="C99" s="38" t="s">
-        <v>175</v>
+        <v>224</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>205</v>
+        <v>124</v>
       </c>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
@@ -3792,7 +4219,7 @@
         <v>253</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>205</v>
@@ -3803,7 +4230,7 @@
         <v>253</v>
       </c>
       <c r="C101" s="38" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>205</v>
@@ -3814,7 +4241,7 @@
         <v>253</v>
       </c>
       <c r="C102" s="38" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>205</v>
@@ -3825,7 +4252,7 @@
         <v>253</v>
       </c>
       <c r="C103" s="38" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>205</v>
@@ -3836,7 +4263,7 @@
         <v>253</v>
       </c>
       <c r="C104" s="38" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>205</v>
@@ -3847,7 +4274,7 @@
         <v>253</v>
       </c>
       <c r="C105" s="38" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>205</v>
@@ -3858,7 +4285,7 @@
         <v>253</v>
       </c>
       <c r="C106" s="38" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>205</v>
@@ -3869,7 +4296,7 @@
         <v>253</v>
       </c>
       <c r="C107" s="38" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>205</v>
@@ -3880,7 +4307,7 @@
         <v>253</v>
       </c>
       <c r="C108" s="38" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>205</v>
@@ -3891,7 +4318,7 @@
         <v>253</v>
       </c>
       <c r="C109" s="38" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>205</v>
@@ -3902,7 +4329,7 @@
         <v>253</v>
       </c>
       <c r="C110" s="38" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>205</v>
@@ -3913,7 +4340,7 @@
         <v>253</v>
       </c>
       <c r="C111" s="38" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>205</v>
@@ -3924,7 +4351,7 @@
         <v>253</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>205</v>
@@ -3935,7 +4362,7 @@
         <v>253</v>
       </c>
       <c r="C113" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>205</v>
@@ -3946,7 +4373,7 @@
         <v>253</v>
       </c>
       <c r="C114" s="38" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>205</v>
@@ -3957,7 +4384,7 @@
         <v>253</v>
       </c>
       <c r="C115" s="38" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>205</v>
@@ -3968,7 +4395,7 @@
         <v>253</v>
       </c>
       <c r="C116" s="38" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>205</v>
@@ -3979,7 +4406,7 @@
         <v>253</v>
       </c>
       <c r="C117" s="38" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>205</v>
@@ -3990,7 +4417,7 @@
         <v>253</v>
       </c>
       <c r="C118" s="38" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>205</v>
@@ -4001,7 +4428,7 @@
         <v>253</v>
       </c>
       <c r="C119" s="38" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>205</v>
@@ -4012,7 +4439,7 @@
         <v>253</v>
       </c>
       <c r="C120" s="38" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>205</v>
@@ -4023,7 +4450,7 @@
         <v>253</v>
       </c>
       <c r="C121" s="38" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>205</v>
@@ -4034,7 +4461,7 @@
         <v>253</v>
       </c>
       <c r="C122" s="38" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>205</v>
@@ -4045,7 +4472,7 @@
         <v>253</v>
       </c>
       <c r="C123" s="38" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>205</v>
@@ -4056,7 +4483,7 @@
         <v>253</v>
       </c>
       <c r="C124" s="38" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>205</v>
@@ -4067,7 +4494,7 @@
         <v>253</v>
       </c>
       <c r="C125" s="38" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>205</v>
@@ -4078,7 +4505,7 @@
         <v>253</v>
       </c>
       <c r="C126" s="38" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>205</v>
@@ -4089,7 +4516,7 @@
         <v>253</v>
       </c>
       <c r="C127" s="38" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>205</v>
@@ -4100,7 +4527,7 @@
         <v>253</v>
       </c>
       <c r="C128" s="38" t="s">
-        <v>308</v>
+        <v>201</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>205</v>
@@ -4108,57 +4535,57 @@
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B129" s="38" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C129" s="38" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B130" s="38" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C130" s="38" t="s">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131" s="38" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C131" s="38" t="s">
-        <v>238</v>
+        <v>308</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="38" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C132" s="38" t="s">
-        <v>239</v>
+        <v>145</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>237</v>
+        <v>162</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133" s="38" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C133" s="38" t="s">
-        <v>236</v>
+        <v>161</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>237</v>
+        <v>162</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
@@ -4166,43 +4593,43 @@
         <v>251</v>
       </c>
       <c r="C134" s="38" t="s">
-        <v>172</v>
+        <v>238</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>22</v>
+        <v>237</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="38" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C135" s="38" t="s">
-        <v>149</v>
+        <v>239</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>152</v>
+        <v>237</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="38" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C136" s="38" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>152</v>
+        <v>237</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="38" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C137" s="38" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
@@ -4210,10 +4637,10 @@
         <v>254</v>
       </c>
       <c r="C138" s="38" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
@@ -4221,10 +4648,10 @@
         <v>254</v>
       </c>
       <c r="C139" s="38" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
@@ -4232,10 +4659,10 @@
         <v>254</v>
       </c>
       <c r="C140" s="38" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
@@ -4243,7 +4670,7 @@
         <v>254</v>
       </c>
       <c r="C141" s="38" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>146</v>
@@ -4254,7 +4681,7 @@
         <v>254</v>
       </c>
       <c r="C142" s="38" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>146</v>
@@ -4265,7 +4692,7 @@
         <v>254</v>
       </c>
       <c r="C143" s="38" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>146</v>
@@ -4276,7 +4703,7 @@
         <v>254</v>
       </c>
       <c r="C144" s="38" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>146</v>
@@ -4287,19 +4714,18 @@
         <v>254</v>
       </c>
       <c r="C145" s="38" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E145" s="4"/>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B146" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C146" s="38" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>146</v>
@@ -4307,35 +4733,36 @@
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B147" s="38" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C147" s="38" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B148" s="38" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C148" s="38" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>171</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="E148" s="4"/>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B149" s="38" t="s">
-        <v>255</v>
-      </c>
-      <c r="C149" s="16" t="s">
-        <v>213</v>
+        <v>254</v>
+      </c>
+      <c r="C149" s="38" t="s">
+        <v>139</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.25">
@@ -4343,7 +4770,7 @@
         <v>255</v>
       </c>
       <c r="C150" s="38" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>171</v>
@@ -4351,40 +4778,49 @@
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B151" s="38" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C151" s="38" t="s">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>437</v>
+        <v>171</v>
       </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B152" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>155</v>
+        <v>255</v>
+      </c>
+      <c r="C152" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B153" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>156</v>
+        <v>255</v>
+      </c>
+      <c r="C153" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B154" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>303</v>
+        <v>252</v>
+      </c>
+      <c r="C154" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.25">
@@ -4392,53 +4828,47 @@
         <v>256</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>304</v>
+        <v>155</v>
       </c>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B156" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="C156" s="38" t="s">
-        <v>211</v>
+        <v>256</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B157" s="38" t="s">
-        <v>245</v>
-      </c>
-      <c r="C157" s="38" t="s">
-        <v>309</v>
+        <v>256</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B158" s="38" t="s">
-        <v>252</v>
-      </c>
-      <c r="C158" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>327</v>
+        <v>256</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B159" s="38" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="C159" s="38" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B160" s="38" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C160" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>223</v>
+        <v>309</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
@@ -4446,21 +4876,18 @@
         <v>252</v>
       </c>
       <c r="C161" s="38" t="s">
-        <v>321</v>
+        <v>216</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>223</v>
+        <v>327</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B162" s="38" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C162" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>223</v>
+        <v>257</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
@@ -4468,7 +4895,7 @@
         <v>252</v>
       </c>
       <c r="C163" s="38" t="s">
-        <v>221</v>
+        <v>320</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>223</v>
@@ -4479,7 +4906,7 @@
         <v>252</v>
       </c>
       <c r="C164" s="38" t="s">
-        <v>222</v>
+        <v>321</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>223</v>
@@ -4487,48 +4914,54 @@
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="38" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C165" s="38" t="s">
-        <v>260</v>
+        <v>322</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>117</v>
+        <v>223</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="38" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C166" s="38" t="s">
-        <v>243</v>
+        <v>221</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="38" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C167" s="38" t="s">
-        <v>164</v>
+        <v>222</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="38" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C168" s="38" t="s">
-        <v>165</v>
+        <v>260</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="38" t="s">
-        <v>317</v>
+        <v>254</v>
       </c>
       <c r="C169" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
@@ -4536,10 +4969,7 @@
         <v>254</v>
       </c>
       <c r="C170" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
@@ -4547,21 +4977,18 @@
         <v>254</v>
       </c>
       <c r="C171" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="38" t="s">
-        <v>254</v>
+        <v>317</v>
       </c>
       <c r="C172" s="38" t="s">
-        <v>164</v>
+        <v>259</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
@@ -4569,7 +4996,7 @@
         <v>254</v>
       </c>
       <c r="C173" s="38" t="s">
-        <v>138</v>
+        <v>261</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>146</v>
@@ -4580,7 +5007,7 @@
         <v>254</v>
       </c>
       <c r="C174" s="38" t="s">
-        <v>262</v>
+        <v>137</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>146</v>
@@ -4591,7 +5018,7 @@
         <v>254</v>
       </c>
       <c r="C175" s="38" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>146</v>
@@ -4602,194 +5029,185 @@
         <v>254</v>
       </c>
       <c r="C176" s="38" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C177" s="38" t="s">
-        <v>143</v>
+        <v>262</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B178" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C178" s="38" t="s">
-        <v>263</v>
+        <v>141</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B179" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C179" s="38" t="s">
-        <v>264</v>
+        <v>142</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B180" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C180" s="38" t="s">
-        <v>265</v>
+        <v>143</v>
       </c>
       <c r="D180" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B181" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C181" s="38" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B182" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C182" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D182" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B183" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C183" s="38" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B184" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C184" s="38" t="s">
-        <v>140</v>
+        <v>266</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B185" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C185" s="38" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B186" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C186" s="38" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B187" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C187" s="38" t="s">
-        <v>271</v>
+        <v>140</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B188" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C188" s="38" t="s">
-        <v>139</v>
+        <v>269</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B189" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C189" s="38" t="s">
-        <v>144</v>
+        <v>270</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B190" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C190" s="38" t="s">
-        <v>149</v>
+        <v>271</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E190" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B191" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C191" s="38" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E191" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B192" s="38" t="s">
         <v>254</v>
       </c>
       <c r="C192" s="38" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E192" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4798,9 +5216,12 @@
         <v>254</v>
       </c>
       <c r="C193" s="38" t="s">
-        <v>272</v>
+        <v>149</v>
       </c>
       <c r="D193" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4809,9 +5230,12 @@
         <v>254</v>
       </c>
       <c r="C194" s="38" t="s">
-        <v>243</v>
+        <v>150</v>
       </c>
       <c r="D194" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4820,9 +5244,12 @@
         <v>254</v>
       </c>
       <c r="C195" s="38" t="s">
-        <v>273</v>
+        <v>151</v>
       </c>
       <c r="D195" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E195" s="1" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4831,7 +5258,7 @@
         <v>254</v>
       </c>
       <c r="C196" s="38" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>146</v>
@@ -4842,7 +5269,7 @@
         <v>254</v>
       </c>
       <c r="C197" s="38" t="s">
-        <v>166</v>
+        <v>243</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>146</v>
@@ -4853,7 +5280,7 @@
         <v>254</v>
       </c>
       <c r="C198" s="38" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>146</v>
@@ -4864,7 +5291,7 @@
         <v>254</v>
       </c>
       <c r="C199" s="38" t="s">
-        <v>274</v>
+        <v>165</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>146</v>
@@ -4875,7 +5302,7 @@
         <v>254</v>
       </c>
       <c r="C200" s="38" t="s">
-        <v>275</v>
+        <v>166</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>146</v>
@@ -4886,7 +5313,7 @@
         <v>254</v>
       </c>
       <c r="C201" s="38" t="s">
-        <v>276</v>
+        <v>167</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>146</v>
@@ -4897,13 +5324,10 @@
         <v>254</v>
       </c>
       <c r="C202" s="38" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>326</v>
+        <v>146</v>
       </c>
     </row>
     <row r="203" spans="2:5" x14ac:dyDescent="0.25">
@@ -4911,13 +5335,10 @@
         <v>254</v>
       </c>
       <c r="C203" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>326</v>
+        <v>146</v>
       </c>
     </row>
     <row r="204" spans="2:5" x14ac:dyDescent="0.25">
@@ -4925,13 +5346,10 @@
         <v>254</v>
       </c>
       <c r="C204" s="38" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>326</v>
+        <v>146</v>
       </c>
     </row>
     <row r="205" spans="2:5" x14ac:dyDescent="0.25">
@@ -4939,7 +5357,7 @@
         <v>254</v>
       </c>
       <c r="C205" s="38" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>301</v>
@@ -4953,7 +5371,7 @@
         <v>254</v>
       </c>
       <c r="C206" s="38" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>301</v>
@@ -4967,7 +5385,7 @@
         <v>254</v>
       </c>
       <c r="C207" s="38" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>301</v>
@@ -4981,7 +5399,7 @@
         <v>254</v>
       </c>
       <c r="C208" s="38" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>301</v>
@@ -4995,7 +5413,7 @@
         <v>254</v>
       </c>
       <c r="C209" s="38" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>301</v>
@@ -5009,7 +5427,7 @@
         <v>254</v>
       </c>
       <c r="C210" s="38" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>301</v>
@@ -5023,7 +5441,7 @@
         <v>254</v>
       </c>
       <c r="C211" s="38" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>301</v>
@@ -5037,7 +5455,7 @@
         <v>254</v>
       </c>
       <c r="C212" s="38" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>301</v>
@@ -5051,7 +5469,7 @@
         <v>254</v>
       </c>
       <c r="C213" s="38" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>301</v>
@@ -5065,7 +5483,7 @@
         <v>254</v>
       </c>
       <c r="C214" s="38" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>301</v>
@@ -5079,7 +5497,7 @@
         <v>254</v>
       </c>
       <c r="C215" s="38" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>301</v>
@@ -5093,7 +5511,7 @@
         <v>254</v>
       </c>
       <c r="C216" s="38" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>301</v>
@@ -5107,7 +5525,7 @@
         <v>254</v>
       </c>
       <c r="C217" s="38" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>301</v>
@@ -5121,7 +5539,7 @@
         <v>254</v>
       </c>
       <c r="C218" s="38" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>301</v>
@@ -5135,7 +5553,7 @@
         <v>254</v>
       </c>
       <c r="C219" s="38" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>301</v>
@@ -5149,7 +5567,7 @@
         <v>254</v>
       </c>
       <c r="C220" s="38" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>301</v>
@@ -5163,7 +5581,7 @@
         <v>254</v>
       </c>
       <c r="C221" s="38" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>301</v>
@@ -5177,7 +5595,7 @@
         <v>254</v>
       </c>
       <c r="C222" s="38" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>301</v>
@@ -5191,7 +5609,7 @@
         <v>254</v>
       </c>
       <c r="C223" s="38" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>301</v>
@@ -5205,7 +5623,7 @@
         <v>254</v>
       </c>
       <c r="C224" s="38" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>301</v>
@@ -5219,7 +5637,7 @@
         <v>254</v>
       </c>
       <c r="C225" s="38" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>301</v>
@@ -5230,46 +5648,55 @@
     </row>
     <row r="226" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B226" s="38" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C226" s="38" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>118</v>
+        <v>301</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="227" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B227" s="38" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C227" s="38" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>258</v>
+        <v>301</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="228" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B228" s="38" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C228" s="38" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>258</v>
+        <v>301</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="229" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B229" s="38" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C229" s="38" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>258</v>
+        <v>118</v>
       </c>
     </row>
     <row r="230" spans="2:5" x14ac:dyDescent="0.25">
@@ -5277,7 +5704,7 @@
         <v>256</v>
       </c>
       <c r="C230" s="38" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>258</v>
@@ -5288,7 +5715,7 @@
         <v>256</v>
       </c>
       <c r="C231" s="38" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>258</v>
@@ -5299,7 +5726,7 @@
         <v>256</v>
       </c>
       <c r="C232" s="38" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>258</v>
@@ -5310,7 +5737,7 @@
         <v>256</v>
       </c>
       <c r="C233" s="38" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>258</v>
@@ -5320,8 +5747,8 @@
       <c r="B234" s="38" t="s">
         <v>256</v>
       </c>
-      <c r="C234" s="16" t="s">
-        <v>314</v>
+      <c r="C234" s="38" t="s">
+        <v>313</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>258</v>
@@ -5329,46 +5756,46 @@
     </row>
     <row r="235" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B235" s="38" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C235" s="38" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
     </row>
     <row r="236" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B236" s="38" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C236" s="38" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>370</v>
+        <v>258</v>
       </c>
     </row>
     <row r="237" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B237" s="38" t="s">
-        <v>254</v>
-      </c>
-      <c r="C237" s="38" t="s">
-        <v>329</v>
+        <v>256</v>
+      </c>
+      <c r="C237" s="16" t="s">
+        <v>314</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>370</v>
+        <v>258</v>
       </c>
     </row>
     <row r="238" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B238" s="38" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C238" s="38" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>370</v>
+        <v>226</v>
       </c>
     </row>
     <row r="239" spans="2:5" x14ac:dyDescent="0.25">
@@ -5376,7 +5803,7 @@
         <v>254</v>
       </c>
       <c r="C239" s="38" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>370</v>
@@ -5387,7 +5814,7 @@
         <v>254</v>
       </c>
       <c r="C240" s="38" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>370</v>
@@ -5398,7 +5825,7 @@
         <v>254</v>
       </c>
       <c r="C241" s="38" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>370</v>
@@ -5409,7 +5836,7 @@
         <v>254</v>
       </c>
       <c r="C242" s="38" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>370</v>
@@ -5420,7 +5847,7 @@
         <v>254</v>
       </c>
       <c r="C243" s="38" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>370</v>
@@ -5431,7 +5858,7 @@
         <v>254</v>
       </c>
       <c r="C244" s="38" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>370</v>
@@ -5442,7 +5869,7 @@
         <v>254</v>
       </c>
       <c r="C245" s="38" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>370</v>
@@ -5453,7 +5880,7 @@
         <v>254</v>
       </c>
       <c r="C246" s="38" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>370</v>
@@ -5464,7 +5891,7 @@
         <v>254</v>
       </c>
       <c r="C247" s="38" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>370</v>
@@ -5475,7 +5902,7 @@
         <v>254</v>
       </c>
       <c r="C248" s="38" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>370</v>
@@ -5486,7 +5913,7 @@
         <v>254</v>
       </c>
       <c r="C249" s="38" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>370</v>
@@ -5497,7 +5924,7 @@
         <v>254</v>
       </c>
       <c r="C250" s="38" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>370</v>
@@ -5508,7 +5935,7 @@
         <v>254</v>
       </c>
       <c r="C251" s="38" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>370</v>
@@ -5519,7 +5946,7 @@
         <v>254</v>
       </c>
       <c r="C252" s="38" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>370</v>
@@ -5530,7 +5957,7 @@
         <v>254</v>
       </c>
       <c r="C253" s="38" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>370</v>
@@ -5541,7 +5968,7 @@
         <v>254</v>
       </c>
       <c r="C254" s="38" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>370</v>
@@ -5552,7 +5979,7 @@
         <v>254</v>
       </c>
       <c r="C255" s="38" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>370</v>
@@ -5563,7 +5990,7 @@
         <v>254</v>
       </c>
       <c r="C256" s="38" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>370</v>
@@ -5574,7 +6001,7 @@
         <v>254</v>
       </c>
       <c r="C257" s="38" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>370</v>
@@ -5585,7 +6012,7 @@
         <v>254</v>
       </c>
       <c r="C258" s="38" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>370</v>
@@ -5596,7 +6023,7 @@
         <v>254</v>
       </c>
       <c r="C259" s="38" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>370</v>
@@ -5607,7 +6034,7 @@
         <v>254</v>
       </c>
       <c r="C260" s="38" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>370</v>
@@ -5618,7 +6045,7 @@
         <v>254</v>
       </c>
       <c r="C261" s="38" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>370</v>
@@ -5629,7 +6056,7 @@
         <v>254</v>
       </c>
       <c r="C262" s="38" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>370</v>
@@ -5640,7 +6067,7 @@
         <v>254</v>
       </c>
       <c r="C263" s="38" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>370</v>
@@ -5651,7 +6078,7 @@
         <v>254</v>
       </c>
       <c r="C264" s="38" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>370</v>
@@ -5662,7 +6089,7 @@
         <v>254</v>
       </c>
       <c r="C265" s="38" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>370</v>
@@ -5673,7 +6100,7 @@
         <v>254</v>
       </c>
       <c r="C266" s="38" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>370</v>
@@ -5684,7 +6111,7 @@
         <v>254</v>
       </c>
       <c r="C267" s="38" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>370</v>
@@ -5695,7 +6122,7 @@
         <v>254</v>
       </c>
       <c r="C268" s="38" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>370</v>
@@ -5706,7 +6133,7 @@
         <v>254</v>
       </c>
       <c r="C269" s="38" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>370</v>
@@ -5717,7 +6144,7 @@
         <v>254</v>
       </c>
       <c r="C270" s="38" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>370</v>
@@ -5728,7 +6155,7 @@
         <v>254</v>
       </c>
       <c r="C271" s="38" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>370</v>
@@ -5739,7 +6166,7 @@
         <v>254</v>
       </c>
       <c r="C272" s="38" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>370</v>
@@ -5750,7 +6177,7 @@
         <v>254</v>
       </c>
       <c r="C273" s="38" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>370</v>
@@ -5761,7 +6188,7 @@
         <v>254</v>
       </c>
       <c r="C274" s="38" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>370</v>
@@ -5772,7 +6199,7 @@
         <v>254</v>
       </c>
       <c r="C275" s="38" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>370</v>
@@ -5783,7 +6210,7 @@
         <v>254</v>
       </c>
       <c r="C276" s="38" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>370</v>
@@ -5794,16 +6221,49 @@
         <v>254</v>
       </c>
       <c r="C277" s="38" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>370</v>
       </c>
     </row>
+    <row r="278" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B278" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="C278" s="38" t="s">
+        <v>367</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="279" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B279" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="C279" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="280" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B280" s="38" t="s">
+        <v>254</v>
+      </c>
+      <c r="C280" s="38" t="s">
+        <v>369</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C149 C166:C169 C234" xr:uid="{C50C147E-E78E-412B-BF69-E30F1F8A8BA9}">
-      <formula1>$C$2:$C$435</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C152 C237 C169:C172" xr:uid="{C50C147E-E78E-412B-BF69-E30F1F8A8BA9}">
+      <formula1>$C$2:$C$438</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5816,7 +6276,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4C4980-2E32-446A-8D12-F72C96030166}">
-  <dimension ref="B1:E57"/>
+  <dimension ref="B1:E58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
@@ -5989,24 +6449,22 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="38" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>402</v>
+        <v>525</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>387</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="38" t="s">
         <v>385</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>386</v>
@@ -6020,7 +6478,7 @@
         <v>385</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>386</v>
@@ -6034,7 +6492,7 @@
         <v>385</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>386</v>
@@ -6048,7 +6506,7 @@
         <v>385</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>386</v>
@@ -6062,7 +6520,7 @@
         <v>385</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>386</v>
@@ -6076,7 +6534,7 @@
         <v>385</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>386</v>
@@ -6090,7 +6548,7 @@
         <v>385</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>386</v>
@@ -6104,7 +6562,7 @@
         <v>385</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>371</v>
+        <v>409</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>386</v>
@@ -6118,7 +6576,7 @@
         <v>385</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>410</v>
+        <v>371</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>386</v>
@@ -6132,7 +6590,7 @@
         <v>385</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>386</v>
@@ -6146,7 +6604,7 @@
         <v>385</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>386</v>
@@ -6160,7 +6618,7 @@
         <v>385</v>
       </c>
       <c r="C25" s="38" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>386</v>
@@ -6174,7 +6632,7 @@
         <v>385</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>386</v>
@@ -6188,7 +6646,7 @@
         <v>385</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>386</v>
@@ -6202,7 +6660,7 @@
         <v>385</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>386</v>
@@ -6216,7 +6674,7 @@
         <v>385</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>386</v>
@@ -6230,7 +6688,7 @@
         <v>385</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>386</v>
@@ -6244,7 +6702,7 @@
         <v>385</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>386</v>
@@ -6258,7 +6716,7 @@
         <v>385</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>386</v>
@@ -6272,7 +6730,7 @@
         <v>385</v>
       </c>
       <c r="C33" s="38" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>386</v>
@@ -6286,7 +6744,7 @@
         <v>385</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>386</v>
@@ -6300,7 +6758,7 @@
         <v>385</v>
       </c>
       <c r="C35" s="38" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>386</v>
@@ -6314,7 +6772,7 @@
         <v>385</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>386</v>
@@ -6328,7 +6786,7 @@
         <v>385</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>386</v>
@@ -6342,7 +6800,7 @@
         <v>385</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>386</v>
@@ -6356,7 +6814,7 @@
         <v>385</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>386</v>
@@ -6370,7 +6828,7 @@
         <v>385</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>386</v>
@@ -6384,7 +6842,7 @@
         <v>385</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>386</v>
@@ -6398,7 +6856,7 @@
         <v>385</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>386</v>
@@ -6412,22 +6870,24 @@
         <v>385</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>215</v>
+        <v>436</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="E43" s="1"/>
+      <c r="E43" s="1" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="38" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C44" s="38" t="s">
-        <v>398</v>
+        <v>215</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E44" s="1"/>
     </row>
@@ -6436,7 +6896,7 @@
         <v>388</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>389</v>
@@ -6448,7 +6908,7 @@
         <v>388</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>389</v>
@@ -6460,7 +6920,7 @@
         <v>388</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>389</v>
@@ -6472,7 +6932,7 @@
         <v>388</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>389</v>
@@ -6481,24 +6941,22 @@
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="38" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>169</v>
+        <v>417</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>392</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="E49" s="1"/>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="38" t="s">
         <v>390</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>171</v>
@@ -6512,7 +6970,7 @@
         <v>390</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>171</v>
@@ -6526,7 +6984,7 @@
         <v>390</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>171</v>
@@ -6537,9 +6995,11 @@
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="38" t="s">
-        <v>391</v>
-      </c>
-      <c r="C53" s="38"/>
+        <v>390</v>
+      </c>
+      <c r="C53" s="38" t="s">
+        <v>214</v>
+      </c>
       <c r="D53" s="1" t="s">
         <v>171</v>
       </c>
@@ -6549,34 +7009,32 @@
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="38" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C54" s="38"/>
       <c r="D54" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E54" s="1"/>
+        <v>171</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="C55" s="38" t="s">
-        <v>400</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="C55" s="38"/>
       <c r="D55" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>397</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="E55" s="1"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="38" t="s">
         <v>395</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>396</v>
@@ -6590,12 +7048,26 @@
         <v>395</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="38" t="s">
+        <v>395</v>
+      </c>
+      <c r="C58" s="38" t="s">
+        <v>419</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>397</v>
       </c>
     </row>
@@ -23127,532 +23599,732 @@
       </c>
     </row>
     <row r="261" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A261" s="26"/>
+      <c r="A261" s="26">
+        <v>46238</v>
+      </c>
       <c r="B261" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C261" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C261" s="16" t="s">
+        <v>105</v>
+      </c>
       <c r="D261" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E261" s="27"/>
-      <c r="F261" s="28"/>
-      <c r="G261" s="27"/>
-      <c r="H261" s="29"/>
-      <c r="I261" s="30" t="e">
+        <v>Embalaje</v>
+      </c>
+      <c r="E261" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="F261" s="28">
+        <v>300</v>
+      </c>
+      <c r="G261" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H261" s="29">
+        <v>1209.380165</v>
+      </c>
+      <c r="I261" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J261" s="31"/>
-      <c r="K261" s="27"/>
-      <c r="L261" s="31"/>
+        <v>0.79827073597359743</v>
+      </c>
+      <c r="J261" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="K261" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L261" s="23">
+        <v>0.21</v>
+      </c>
       <c r="M261" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N261" s="51" t="e">
+        <v>326532.64455000003</v>
+      </c>
+      <c r="N261" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>215.53309871287129</v>
       </c>
       <c r="O261" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P261" s="33" t="e">
+        <v>395104.49990550004</v>
+      </c>
+      <c r="P261" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>260.79504944257428</v>
       </c>
       <c r="Q261" s="34">
         <f>_xlfn.XLOOKUP(A261,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
+        <v>1515</v>
       </c>
       <c r="R261" s="16"/>
     </row>
     <row r="262" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A262" s="26"/>
+      <c r="A262" s="26">
+        <v>46239</v>
+      </c>
       <c r="B262" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C262" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C262" s="16" t="s">
+        <v>54</v>
+      </c>
       <c r="D262" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E262" s="27"/>
-      <c r="F262" s="28"/>
-      <c r="G262" s="27"/>
-      <c r="H262" s="29"/>
-      <c r="I262" s="30" t="e">
+        <v>Embalaje</v>
+      </c>
+      <c r="E262" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F262" s="28">
+        <v>30</v>
+      </c>
+      <c r="G262" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="H262" s="29">
+        <v>22939.22</v>
+      </c>
+      <c r="I262" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J262" s="31"/>
-      <c r="K262" s="27"/>
-      <c r="L262" s="31"/>
+        <v>15.091592105263159</v>
+      </c>
+      <c r="J262" s="31">
+        <v>0.4</v>
+      </c>
+      <c r="K262" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L262" s="23">
+        <v>0.21</v>
+      </c>
       <c r="M262" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N262" s="51" t="e">
+        <v>412905.96</v>
+      </c>
+      <c r="N262" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>271.64865789473686</v>
       </c>
       <c r="O262" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P262" s="33" t="e">
+        <v>499616.21160000004</v>
+      </c>
+      <c r="P262" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>328.69487605263163</v>
       </c>
       <c r="Q262" s="34">
         <f>_xlfn.XLOOKUP(A262,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
-      </c>
-      <c r="R262" s="16"/>
+        <v>1520</v>
+      </c>
+      <c r="R262" s="16" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A263" s="26"/>
+      <c r="A263" s="26">
+        <v>46240</v>
+      </c>
       <c r="B263" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C263" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C263" s="16" t="s">
+        <v>530</v>
+      </c>
       <c r="D263" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E263" s="27"/>
-      <c r="F263" s="28"/>
-      <c r="G263" s="27"/>
-      <c r="H263" s="29"/>
-      <c r="I263" s="30" t="e">
+        <v>Farmacia</v>
+      </c>
+      <c r="E263" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="F263" s="28">
+        <v>1</v>
+      </c>
+      <c r="G263" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H263" s="29">
+        <v>2107.44</v>
+      </c>
+      <c r="I263" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J263" s="31"/>
-      <c r="K263" s="27"/>
-      <c r="L263" s="31"/>
+        <v>1.3864736842105263</v>
+      </c>
+      <c r="J263" s="31">
+        <v>0</v>
+      </c>
+      <c r="K263" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L263" s="23"/>
       <c r="M263" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N263" s="51" t="e">
+        <v>2107.44</v>
+      </c>
+      <c r="N263" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>1.3864736842105263</v>
       </c>
       <c r="O263" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P263" s="33" t="e">
+        <v>2107.44</v>
+      </c>
+      <c r="P263" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>1.3864736842105263</v>
       </c>
       <c r="Q263" s="34">
         <f>_xlfn.XLOOKUP(A263,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
+        <v>1520</v>
       </c>
       <c r="R263" s="16"/>
     </row>
     <row r="264" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A264" s="26"/>
+      <c r="A264" s="26">
+        <v>46240</v>
+      </c>
       <c r="B264" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C264" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C264" s="16" t="s">
+        <v>530</v>
+      </c>
       <c r="D264" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E264" s="27"/>
-      <c r="F264" s="28"/>
-      <c r="G264" s="27"/>
-      <c r="H264" s="29"/>
-      <c r="I264" s="30" t="e">
+        <v>Farmacia</v>
+      </c>
+      <c r="E264" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="F264" s="28">
+        <v>1</v>
+      </c>
+      <c r="G264" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H264" s="29">
+        <v>7727.27</v>
+      </c>
+      <c r="I264" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J264" s="31"/>
-      <c r="K264" s="27"/>
-      <c r="L264" s="31"/>
+        <v>5.0837302631578947</v>
+      </c>
+      <c r="J264" s="31">
+        <v>0</v>
+      </c>
+      <c r="K264" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L264" s="23"/>
       <c r="M264" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N264" s="51" t="e">
+        <v>7727.27</v>
+      </c>
+      <c r="N264" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>5.0837302631578947</v>
       </c>
       <c r="O264" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P264" s="33" t="e">
+        <v>7727.27</v>
+      </c>
+      <c r="P264" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>5.0837302631578947</v>
       </c>
       <c r="Q264" s="34">
         <f>_xlfn.XLOOKUP(A264,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
+        <v>1520</v>
       </c>
       <c r="R264" s="16"/>
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A265" s="27"/>
+      <c r="A265" s="26">
+        <v>46240</v>
+      </c>
       <c r="B265" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C265" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C265" s="16" t="s">
+        <v>530</v>
+      </c>
       <c r="D265" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E265" s="27"/>
-      <c r="F265" s="28"/>
-      <c r="G265" s="27"/>
-      <c r="H265" s="29"/>
-      <c r="I265" s="30" t="e">
+        <v>Farmacia</v>
+      </c>
+      <c r="E265" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="F265" s="28">
+        <v>1</v>
+      </c>
+      <c r="G265" s="27" t="s">
+        <v>529</v>
+      </c>
+      <c r="H265" s="29">
+        <v>22479.34</v>
+      </c>
+      <c r="I265" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J265" s="31"/>
-      <c r="K265" s="27"/>
-      <c r="L265" s="31"/>
+        <v>14.789039473684211</v>
+      </c>
+      <c r="J265" s="31">
+        <v>0</v>
+      </c>
+      <c r="K265" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L265" s="23"/>
       <c r="M265" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N265" s="51" t="e">
+        <v>22479.34</v>
+      </c>
+      <c r="N265" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>14.789039473684211</v>
       </c>
       <c r="O265" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P265" s="33" t="e">
+        <v>22479.34</v>
+      </c>
+      <c r="P265" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>14.789039473684211</v>
       </c>
       <c r="Q265" s="34">
         <f>_xlfn.XLOOKUP(A265,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
+        <v>1520</v>
       </c>
       <c r="R265" s="16"/>
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A266" s="27"/>
+      <c r="A266" s="26">
+        <v>46240</v>
+      </c>
       <c r="B266" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C266" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C266" s="16" t="s">
+        <v>530</v>
+      </c>
       <c r="D266" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E266" s="27"/>
-      <c r="F266" s="28"/>
-      <c r="G266" s="27"/>
-      <c r="H266" s="29"/>
-      <c r="I266" s="30" t="e">
+        <v>Farmacia</v>
+      </c>
+      <c r="E266" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="F266" s="28">
+        <v>1</v>
+      </c>
+      <c r="G266" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H266" s="29">
+        <v>4214.88</v>
+      </c>
+      <c r="I266" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J266" s="31"/>
-      <c r="K266" s="27"/>
-      <c r="L266" s="31"/>
+        <v>2.7729473684210526</v>
+      </c>
+      <c r="J266" s="31">
+        <v>0</v>
+      </c>
+      <c r="K266" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L266" s="23"/>
       <c r="M266" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N266" s="51" t="e">
+        <v>4214.88</v>
+      </c>
+      <c r="N266" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>2.7729473684210526</v>
       </c>
       <c r="O266" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P266" s="33" t="e">
+        <v>4214.88</v>
+      </c>
+      <c r="P266" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>2.7729473684210526</v>
       </c>
       <c r="Q266" s="34">
         <f>_xlfn.XLOOKUP(A266,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
+        <v>1520</v>
       </c>
       <c r="R266" s="16"/>
     </row>
     <row r="267" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A267" s="27"/>
+      <c r="A267" s="26">
+        <v>46240</v>
+      </c>
       <c r="B267" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C267" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C267" s="16" t="s">
+        <v>530</v>
+      </c>
       <c r="D267" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E267" s="27"/>
-      <c r="F267" s="28"/>
-      <c r="G267" s="27"/>
-      <c r="H267" s="29"/>
-      <c r="I267" s="30" t="e">
+        <v>Farmacia</v>
+      </c>
+      <c r="E267" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="F267" s="28">
+        <v>1</v>
+      </c>
+      <c r="G267" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H267" s="29">
+        <v>4214.88</v>
+      </c>
+      <c r="I267" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J267" s="31"/>
-      <c r="K267" s="27"/>
-      <c r="L267" s="31"/>
+        <v>2.7729473684210526</v>
+      </c>
+      <c r="J267" s="31">
+        <v>0</v>
+      </c>
+      <c r="K267" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L267" s="23"/>
       <c r="M267" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N267" s="51" t="e">
+        <v>4214.88</v>
+      </c>
+      <c r="N267" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>2.7729473684210526</v>
       </c>
       <c r="O267" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P267" s="33" t="e">
+        <v>4214.88</v>
+      </c>
+      <c r="P267" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>2.7729473684210526</v>
       </c>
       <c r="Q267" s="34">
         <f>_xlfn.XLOOKUP(A267,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
+        <v>1520</v>
       </c>
       <c r="R267" s="16"/>
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A268" s="27"/>
+      <c r="A268" s="26">
+        <v>46240</v>
+      </c>
       <c r="B268" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C268" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C268" s="16" t="s">
+        <v>527</v>
+      </c>
       <c r="D268" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E268" s="27"/>
-      <c r="F268" s="28"/>
-      <c r="G268" s="27"/>
-      <c r="H268" s="29"/>
-      <c r="I268" s="30" t="e">
+        <v>Farmacia</v>
+      </c>
+      <c r="E268" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="F268" s="28">
+        <v>1</v>
+      </c>
+      <c r="G268" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H268" s="29">
+        <v>6800</v>
+      </c>
+      <c r="I268" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J268" s="31"/>
-      <c r="K268" s="27"/>
-      <c r="L268" s="31"/>
+        <v>4.4736842105263159</v>
+      </c>
+      <c r="J268" s="31">
+        <v>0</v>
+      </c>
+      <c r="K268" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L268" s="23"/>
       <c r="M268" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N268" s="51" t="e">
+        <v>6800</v>
+      </c>
+      <c r="N268" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>4.4736842105263159</v>
       </c>
       <c r="O268" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P268" s="33" t="e">
+        <v>6800</v>
+      </c>
+      <c r="P268" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>4.4736842105263159</v>
       </c>
       <c r="Q268" s="34">
         <f>_xlfn.XLOOKUP(A268,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
+        <v>1520</v>
       </c>
       <c r="R268" s="16"/>
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A269" s="27"/>
+      <c r="A269" s="26">
+        <v>46240</v>
+      </c>
       <c r="B269" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C269" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C269" s="16" t="s">
+        <v>527</v>
+      </c>
       <c r="D269" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E269" s="27"/>
-      <c r="F269" s="28"/>
-      <c r="G269" s="27"/>
-      <c r="H269" s="29"/>
-      <c r="I269" s="30" t="e">
+        <v>Farmacia</v>
+      </c>
+      <c r="E269" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="F269" s="28">
+        <v>1</v>
+      </c>
+      <c r="G269" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H269" s="29">
+        <v>8550</v>
+      </c>
+      <c r="I269" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J269" s="31"/>
-      <c r="K269" s="27"/>
-      <c r="L269" s="31"/>
+        <v>5.625</v>
+      </c>
+      <c r="J269" s="31">
+        <v>0</v>
+      </c>
+      <c r="K269" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L269" s="23"/>
       <c r="M269" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N269" s="51" t="e">
+        <v>8550</v>
+      </c>
+      <c r="N269" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>5.625</v>
       </c>
       <c r="O269" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P269" s="33" t="e">
+        <v>8550</v>
+      </c>
+      <c r="P269" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>5.625</v>
       </c>
       <c r="Q269" s="34">
         <f>_xlfn.XLOOKUP(A269,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
+        <v>1520</v>
       </c>
       <c r="R269" s="16"/>
     </row>
     <row r="270" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A270" s="27"/>
+      <c r="A270" s="26">
+        <v>46240</v>
+      </c>
       <c r="B270" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C270" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C270" s="16" t="s">
+        <v>527</v>
+      </c>
       <c r="D270" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E270" s="27"/>
-      <c r="F270" s="28"/>
-      <c r="G270" s="27"/>
-      <c r="H270" s="29"/>
-      <c r="I270" s="30" t="e">
+        <v>Farmacia</v>
+      </c>
+      <c r="E270" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="F270" s="28">
+        <v>1</v>
+      </c>
+      <c r="G270" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H270" s="29">
+        <v>11220</v>
+      </c>
+      <c r="I270" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J270" s="31"/>
-      <c r="K270" s="27"/>
-      <c r="L270" s="31"/>
+        <v>7.3815789473684212</v>
+      </c>
+      <c r="J270" s="31">
+        <v>0</v>
+      </c>
+      <c r="K270" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L270" s="23"/>
       <c r="M270" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N270" s="51" t="e">
+        <v>11220</v>
+      </c>
+      <c r="N270" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>7.3815789473684212</v>
       </c>
       <c r="O270" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P270" s="33" t="e">
+        <v>11220</v>
+      </c>
+      <c r="P270" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>7.3815789473684212</v>
       </c>
       <c r="Q270" s="34">
         <f>_xlfn.XLOOKUP(A270,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
+        <v>1520</v>
       </c>
       <c r="R270" s="16"/>
     </row>
     <row r="271" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A271" s="27"/>
+      <c r="A271" s="26">
+        <v>46240</v>
+      </c>
       <c r="B271" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C271" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C271" s="16" t="s">
+        <v>527</v>
+      </c>
       <c r="D271" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E271" s="27"/>
-      <c r="F271" s="28"/>
-      <c r="G271" s="27"/>
-      <c r="H271" s="29"/>
-      <c r="I271" s="30" t="e">
+        <v>Farmacia</v>
+      </c>
+      <c r="E271" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="F271" s="28">
+        <v>1</v>
+      </c>
+      <c r="G271" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H271" s="29">
+        <v>11900</v>
+      </c>
+      <c r="I271" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J271" s="31"/>
-      <c r="K271" s="27"/>
-      <c r="L271" s="31"/>
+        <v>7.8289473684210522</v>
+      </c>
+      <c r="J271" s="31">
+        <v>0</v>
+      </c>
+      <c r="K271" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L271" s="23"/>
       <c r="M271" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N271" s="51" t="e">
+        <v>11900</v>
+      </c>
+      <c r="N271" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>7.8289473684210522</v>
       </c>
       <c r="O271" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P271" s="33" t="e">
+        <v>11900</v>
+      </c>
+      <c r="P271" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>7.8289473684210522</v>
       </c>
       <c r="Q271" s="34">
         <f>_xlfn.XLOOKUP(A271,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
+        <v>1520</v>
       </c>
       <c r="R271" s="16"/>
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A272" s="27"/>
+      <c r="A272" s="26">
+        <v>46240</v>
+      </c>
       <c r="B272" s="15">
         <f>MONTH(Tabla2[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C272" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C272" s="16" t="s">
+        <v>530</v>
+      </c>
       <c r="D272" s="35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla2[[#This Row],[Artículo]],Tabla1[Artículos],Tabla1[Rubro]),"")</f>
-        <v/>
-      </c>
-      <c r="E272" s="27"/>
-      <c r="F272" s="28"/>
-      <c r="G272" s="27"/>
-      <c r="H272" s="29"/>
-      <c r="I272" s="30" t="e">
+        <v>Farmacia</v>
+      </c>
+      <c r="E272" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="F272" s="28">
+        <v>1</v>
+      </c>
+      <c r="G272" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H272" s="29">
+        <v>8556.2000000000007</v>
+      </c>
+      <c r="I272" s="30">
         <f>Tabla2[[#This Row],[Precio Unitario ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J272" s="31"/>
-      <c r="K272" s="27"/>
+        <v>5.6290789473684217</v>
+      </c>
+      <c r="J272" s="31">
+        <v>0</v>
+      </c>
+      <c r="K272" s="18" t="s">
+        <v>19</v>
+      </c>
       <c r="L272" s="31"/>
       <c r="M272" s="32">
         <f>(Tabla2[[#This Row],[Precio Unitario ARS]]-(Tabla2[[#This Row],[Precio Unitario ARS]]*Tabla2[[#This Row],[DTO]]))*Tabla2[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N272" s="51" t="e">
+        <v>8556.2000000000007</v>
+      </c>
+      <c r="N272" s="51">
         <f>Tabla2[[#This Row],[Subtotal ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>5.6290789473684217</v>
       </c>
       <c r="O272" s="33">
         <f>Tabla2[[#This Row],[Subtotal ARS]]+(Tabla2[[#This Row],[Subtotal ARS]]*Tabla2[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P272" s="33" t="e">
+        <v>8556.2000000000007</v>
+      </c>
+      <c r="P272" s="33">
         <f>Tabla2[[#This Row],[TOTAL ARS]]/Tabla2[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>5.6290789473684217</v>
       </c>
       <c r="Q272" s="34">
         <f>_xlfn.XLOOKUP(A272,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
-      </c>
-      <c r="R272" s="16"/>
+        <v>1520</v>
+      </c>
+      <c r="R272" s="16" t="s">
+        <v>531</v>
+      </c>
     </row>
     <row r="273" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273" s="27"/>
@@ -25832,7 +26504,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0E99E932-C880-4ADB-B3B9-C3486532C7A0}">
           <x14:formula1>
-            <xm:f>'Insumos-materia prima-reventa'!$C$2:$C$435</xm:f>
+            <xm:f>'Insumos-materia prima-reventa'!$C$2:$C$438</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C254 C260:C321</xm:sqref>
         </x14:dataValidation>
@@ -30949,43 +31621,65 @@
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A85" s="1"/>
+      <c r="A85" s="45">
+        <v>46240</v>
+      </c>
       <c r="B85" s="43">
         <f>MONTH(Tabla6[[#This Row],[Fecha]])</f>
-        <v>1</v>
-      </c>
-      <c r="C85" s="16"/>
+        <v>8</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>525</v>
+      </c>
       <c r="D85" s="44" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(Tabla6[[#This Row],[Artículo]],Tabla7[Artículos],Tabla7[Rubro]),"")</f>
-        <v>Servicio - Plegado</v>
-      </c>
-      <c r="F85" s="39"/>
-      <c r="H85" s="40"/>
-      <c r="I85" s="41" t="e">
+        <v>Servicio - Post. Galvanizado</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F85" s="39">
+        <f>73+11</f>
+        <v>84</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H85" s="40">
+        <v>1945.6</v>
+      </c>
+      <c r="I85" s="41">
         <f>Tabla6[[#This Row],[Precio Unitario ARS]]/Tabla6[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J85" s="2"/>
-      <c r="L85" s="2"/>
+        <v>1.28</v>
+      </c>
+      <c r="J85" s="2">
+        <v>0</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L85" s="2">
+        <v>0.21</v>
+      </c>
       <c r="M85" s="42">
         <f>(Tabla6[[#This Row],[Precio Unitario ARS]]-(Tabla6[[#This Row],[Precio Unitario ARS]]*Tabla6[[#This Row],[DTO]]))*Tabla6[[#This Row],[Cantidad]]</f>
-        <v>0</v>
-      </c>
-      <c r="N85" s="48" t="e">
+        <v>163430.39999999999</v>
+      </c>
+      <c r="N85" s="48">
         <f>Tabla6[[#This Row],[Subtotal ARS]]/Tabla6[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>107.52</v>
       </c>
       <c r="O85" s="42">
         <f>Tabla6[[#This Row],[Subtotal ARS]]+(Tabla6[[#This Row],[Subtotal ARS]]*Tabla6[[#This Row],[IVA]])</f>
-        <v>0</v>
-      </c>
-      <c r="P85" s="47" t="e">
+        <v>197750.78399999999</v>
+      </c>
+      <c r="P85" s="47">
         <f>Tabla6[[#This Row],[TOTAL ARS]]/Tabla6[[#This Row],[TC BNA]]</f>
-        <v>#DIV/0!</v>
+        <v>130.0992</v>
       </c>
       <c r="Q85" s="43">
         <f>_xlfn.XLOOKUP(A85,'TC_BNA xlsx'!A:A,'TC_BNA xlsx'!C:C,"No encontrado")</f>
-        <v>0</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -31878,7 +32572,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F5DEEDEF-DD9C-45C3-AB07-A525D199959D}">
           <x14:formula1>
-            <xm:f>'Insumos-materia prima-reventa'!$C$2:$C$435</xm:f>
+            <xm:f>'Insumos-materia prima-reventa'!$C$2:$C$438</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C6</xm:sqref>
         </x14:dataValidation>
@@ -31896,7 +32590,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5C69A471-3308-4E34-B910-15DC55A49443}">
           <x14:formula1>
-            <xm:f>Servicios!$C$2:$C$256</xm:f>
+            <xm:f>Servicios!$C$2:$C$257</xm:f>
           </x14:formula1>
           <xm:sqref>C7:C107</xm:sqref>
         </x14:dataValidation>
@@ -33829,7 +34523,7 @@
       </c>
       <c r="F40" s="7">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(_xlfn.XLOOKUP(Tabla4[[#This Row],[Artículo]],Tabla2[Artículo],Tabla2[Precio Unitario ARS],"",0,-1),""))</f>
-        <v>22056.94</v>
+        <v>22939.22</v>
       </c>
       <c r="G40" s="12" t="str">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(_xlfn.XLOOKUP(Tabla4[[#This Row],[Artículo]],Tabla2[Artículo],Tabla2[Proveedor],"",0,-1),""))</f>
@@ -33845,7 +34539,7 @@
       </c>
       <c r="J40" s="6">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR((Tabla4[[#This Row],[Precio Cotizado]]-Tabla4[[#This Row],[Últ. Precio]])/Tabla4[[#This Row],[Últ. Precio]],""))</f>
-        <v>4.0049979734269624E-2</v>
+        <v>4.7952807462439642E-5</v>
       </c>
       <c r="K40" s="7">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(Tabla4[[#This Row],[Precio Cotizado]]-Tabla4[[#This Row],[Mejor Precio]],""))</f>
@@ -34006,33 +34700,38 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="9">
+        <v>46238</v>
+      </c>
       <c r="B44" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E44" s="37"/>
+        <v>105</v>
+      </c>
+      <c r="E44" s="37">
+        <v>1209.380165</v>
+      </c>
       <c r="F44" s="7">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(_xlfn.XLOOKUP(Tabla4[[#This Row],[Artículo]],Tabla2[Artículo],Tabla2[Precio Unitario ARS],"",0,-1),""))</f>
-        <v>5900</v>
+        <v>1209.380165</v>
       </c>
       <c r="G44" s="12" t="str">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(_xlfn.XLOOKUP(Tabla4[[#This Row],[Artículo]],Tabla2[Artículo],Tabla2[Proveedor],"",0,-1),""))</f>
-        <v>Zicari Mariana Elena</v>
+        <v>Aserradero Alonso</v>
       </c>
       <c r="H44" s="7" cm="1">
         <f t="array" ref="H44">IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(MIN(_xlfn._xlws.FILTER(Tabla2[Precio Unitario ARS],Tabla2[Artículo]=Tabla4[[#This Row],[Artículo]])),""))</f>
-        <v>5800</v>
+        <v>1151.7874999999999</v>
       </c>
       <c r="I44" s="7" t="str" cm="1">
         <f t="array" ref="I44">IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(_xlfn.XLOOKUP(1,(Tabla2[Artículo]=Tabla4[[#This Row],[Artículo]])*(Tabla2[Precio Unitario ARS]=Tabla4[[#This Row],[Mejor Precio]]),Tabla2[Proveedor]),""))</f>
-        <v>Zicari Mariana Elena</v>
+        <v>Aserradero Alonso</v>
       </c>
       <c r="J44" s="6">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR((Tabla4[[#This Row],[Precio Cotizado]]-Tabla4[[#This Row],[Últ. Precio]])/Tabla4[[#This Row],[Últ. Precio]],""))</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="7">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(Tabla4[[#This Row],[Precio Cotizado]]-Tabla4[[#This Row],[Mejor Precio]],""))</f>
-        <v>-5800</v>
+        <v>57.592665000000125</v>
       </c>
       <c r="L44" s="8">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(Tabla4[[#This Row],[Dif por Unidad]]*Tabla4[[#This Row],[Cantidad]],""))</f>
@@ -34040,33 +34739,33 @@
       </c>
       <c r="M44" s="13" t="str">
         <f t="shared" si="1"/>
-        <v>Más barato</v>
+        <v>Dentro del rango</v>
       </c>
       <c r="N44" s="13" t="str">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IF(Tabla4[[#This Row],[Estado]]="Más barato","✓ Conviene comprar. Ahorro respecto al mejor precio.",IF(Tabla4[[#This Row],[Estado]]="Dentro del rango","✓ Precio dentro del rango habitual.",IF(Tabla4[[#This Row],[Estado]]="Revisar","⚠ Solicitar otra cotización.","🚨 Precio elevado. Negociar o buscar alternativa."))))</f>
-        <v>✓ Conviene comprar. Ahorro respecto al mejor precio.</v>
+        <v>✓ Precio dentro del rango habitual.</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="E45" s="37"/>
       <c r="F45" s="7">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(_xlfn.XLOOKUP(Tabla4[[#This Row],[Artículo]],Tabla2[Artículo],Tabla2[Precio Unitario ARS],"",0,-1),""))</f>
-        <v>16720</v>
+        <v>27888.080000000002</v>
       </c>
       <c r="G45" s="12" t="str">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(_xlfn.XLOOKUP(Tabla4[[#This Row],[Artículo]],Tabla2[Artículo],Tabla2[Proveedor],"",0,-1),""))</f>
-        <v>Zicari Mariana Elena</v>
+        <v>Adamat</v>
       </c>
       <c r="H45" s="7" cm="1">
         <f t="array" ref="H45">IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(MIN(_xlfn._xlws.FILTER(Tabla2[Precio Unitario ARS],Tabla2[Artículo]=Tabla4[[#This Row],[Artículo]])),""))</f>
-        <v>15225</v>
+        <v>27888.080000000002</v>
       </c>
       <c r="I45" s="7" t="str" cm="1">
         <f t="array" ref="I45">IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(_xlfn.XLOOKUP(1,(Tabla2[Artículo]=Tabla4[[#This Row],[Artículo]])*(Tabla2[Precio Unitario ARS]=Tabla4[[#This Row],[Mejor Precio]]),Tabla2[Proveedor]),""))</f>
-        <v>Zicari Mariana Elena</v>
+        <v>Adamat</v>
       </c>
       <c r="J45" s="6">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR((Tabla4[[#This Row],[Precio Cotizado]]-Tabla4[[#This Row],[Últ. Precio]])/Tabla4[[#This Row],[Últ. Precio]],""))</f>
@@ -34074,7 +34773,7 @@
       </c>
       <c r="K45" s="7">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(Tabla4[[#This Row],[Precio Cotizado]]-Tabla4[[#This Row],[Mejor Precio]],""))</f>
-        <v>-15225</v>
+        <v>-27888.080000000002</v>
       </c>
       <c r="L45" s="8">
         <f>IF(Tabla4[[#This Row],[Artículo]]="","",IFERROR(Tabla4[[#This Row],[Dif por Unidad]]*Tabla4[[#This Row],[Cantidad]],""))</f>
@@ -34090,6 +34789,7 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" s="9"/>
       <c r="B46" s="1"/>
       <c r="E46" s="37"/>
       <c r="F46" s="7" t="str">
@@ -38744,7 +39444,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4D7343AF-CCA5-402D-935E-EA0E0FE78200}">
           <x14:formula1>
-            <xm:f>'Insumos-materia prima-reventa'!$C$1:$C$461</xm:f>
+            <xm:f>'Insumos-materia prima-reventa'!$C$1:$C$464</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B161</xm:sqref>
         </x14:dataValidation>
@@ -38762,7 +39462,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14D7CA1C-88A6-4466-9EB8-9ADEF10C90A8}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -39496,11 +40196,907 @@
         <v>1515</v>
       </c>
     </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="9">
+        <v>46239</v>
+      </c>
+      <c r="B67" s="3">
+        <v>1470</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="9">
+        <v>46240</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1470</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="9">
+        <v>46241</v>
+      </c>
+      <c r="B69" s="3">
+        <v>1470</v>
+      </c>
+      <c r="C69" s="3">
+        <v>1520</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9282E20-FC66-4CA7-B4A6-D2DC5518663F}">
+  <dimension ref="A2:K46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" style="53"/>
+    <col min="2" max="2" width="16.42578125" style="53" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" style="53" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="53" customWidth="1"/>
+    <col min="6" max="7" width="11.42578125" style="53"/>
+    <col min="8" max="8" width="27.140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.140625" style="53" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" style="53" customWidth="1"/>
+    <col min="11" max="11" width="36.140625" style="53" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="53"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="52"/>
+      <c r="B3" s="72" t="s">
+        <v>441</v>
+      </c>
+      <c r="C3" s="73"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="52"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="54" t="s">
+        <v>442</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="55" t="s">
+        <v>447</v>
+      </c>
+      <c r="E7" s="65" t="s">
+        <v>443</v>
+      </c>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="57" t="s">
+        <v>444</v>
+      </c>
+      <c r="I7" s="57" t="s">
+        <v>445</v>
+      </c>
+      <c r="J7" s="57" t="s">
+        <v>446</v>
+      </c>
+      <c r="K7" s="53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="71" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E8" s="69" t="s">
+        <v>467</v>
+      </c>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="65" t="s">
+        <v>450</v>
+      </c>
+      <c r="I8" s="65" t="s">
+        <v>452</v>
+      </c>
+      <c r="J8" s="68" t="s">
+        <v>453</v>
+      </c>
+      <c r="K8" s="64" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="71"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="63"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="71"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="63"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="71"/>
+      <c r="C11" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="65" t="s">
+        <v>449</v>
+      </c>
+      <c r="E11" s="64" t="s">
+        <v>466</v>
+      </c>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="65" t="s">
+        <v>451</v>
+      </c>
+      <c r="I11" s="68" t="s">
+        <v>454</v>
+      </c>
+      <c r="J11" s="65" t="s">
+        <v>455</v>
+      </c>
+      <c r="K11" s="63"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="71"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="63"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="71"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="63"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="71"/>
+      <c r="C14" s="65" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E14" s="63" t="s">
+        <v>456</v>
+      </c>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
+      <c r="H14" s="65" t="s">
+        <v>457</v>
+      </c>
+      <c r="I14" s="65" t="s">
+        <v>458</v>
+      </c>
+      <c r="J14" s="68" t="s">
+        <v>459</v>
+      </c>
+      <c r="K14" s="68" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="71"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="71"/>
+      <c r="C16" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="56" t="s">
+        <v>449</v>
+      </c>
+      <c r="E16" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="56" t="s">
+        <v>460</v>
+      </c>
+      <c r="I16" s="56" t="s">
+        <v>461</v>
+      </c>
+      <c r="J16" s="61" t="s">
+        <v>462</v>
+      </c>
+      <c r="K16" s="62" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="71"/>
+      <c r="C17" s="65" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E17" s="69" t="s">
+        <v>468</v>
+      </c>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="65" t="s">
+        <v>469</v>
+      </c>
+      <c r="I17" s="64" t="s">
+        <v>470</v>
+      </c>
+      <c r="J17" s="65" t="s">
+        <v>471</v>
+      </c>
+      <c r="K17" s="63" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="71"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="63"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="71"/>
+      <c r="C19" s="65" t="s">
+        <v>473</v>
+      </c>
+      <c r="D19" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>477</v>
+      </c>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="65" t="s">
+        <v>475</v>
+      </c>
+      <c r="I19" s="63" t="s">
+        <v>476</v>
+      </c>
+      <c r="J19" s="65" t="s">
+        <v>471</v>
+      </c>
+      <c r="K19" s="67"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="71"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="67"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="71"/>
+      <c r="C21" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="D21" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E21" s="63" t="s">
+        <v>478</v>
+      </c>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="65" t="s">
+        <v>479</v>
+      </c>
+      <c r="I21" s="64" t="s">
+        <v>480</v>
+      </c>
+      <c r="J21" s="65" t="s">
+        <v>481</v>
+      </c>
+      <c r="K21" s="67"/>
+    </row>
+    <row r="22" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="71"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="67"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="71"/>
+      <c r="C23" s="65" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E23" s="63" t="s">
+        <v>482</v>
+      </c>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="65" t="s">
+        <v>483</v>
+      </c>
+      <c r="I23" s="63" t="s">
+        <v>484</v>
+      </c>
+      <c r="J23" s="65" t="s">
+        <v>481</v>
+      </c>
+      <c r="K23" s="67"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="71"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="67"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="71"/>
+      <c r="C25" s="65" t="s">
+        <v>486</v>
+      </c>
+      <c r="D25" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E25" s="63" t="s">
+        <v>485</v>
+      </c>
+      <c r="F25" s="63"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="65" t="s">
+        <v>487</v>
+      </c>
+      <c r="I25" s="69" t="s">
+        <v>488</v>
+      </c>
+      <c r="J25" s="68" t="s">
+        <v>489</v>
+      </c>
+      <c r="K25" s="63"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B26" s="71"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="63"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="71"/>
+      <c r="C27" s="67" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="67" t="s">
+        <v>448</v>
+      </c>
+      <c r="E27" s="70" t="s">
+        <v>490</v>
+      </c>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="67" t="s">
+        <v>491</v>
+      </c>
+      <c r="I27" s="69" t="s">
+        <v>492</v>
+      </c>
+      <c r="J27" s="67" t="s">
+        <v>471</v>
+      </c>
+      <c r="K27" s="67"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="71"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C29" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E29" s="63" t="s">
+        <v>493</v>
+      </c>
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="I29" s="64" t="s">
+        <v>495</v>
+      </c>
+      <c r="J29" s="68" t="s">
+        <v>496</v>
+      </c>
+      <c r="K29" s="67"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="63"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="65"/>
+      <c r="K30" s="67"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C31" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E31" s="63" t="s">
+        <v>497</v>
+      </c>
+      <c r="F31" s="63"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="65" t="s">
+        <v>498</v>
+      </c>
+      <c r="I31" s="69" t="s">
+        <v>499</v>
+      </c>
+      <c r="J31" s="65" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C32" s="65"/>
+      <c r="D32" s="65"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="70"/>
+      <c r="J32" s="65"/>
+    </row>
+    <row r="33" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C33" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E33" s="63" t="s">
+        <v>500</v>
+      </c>
+      <c r="F33" s="63"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="65" t="s">
+        <v>501</v>
+      </c>
+      <c r="I33" s="63" t="s">
+        <v>502</v>
+      </c>
+      <c r="J33" s="68" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="34" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="63"/>
+      <c r="F34" s="63"/>
+      <c r="G34" s="63"/>
+      <c r="H34" s="65"/>
+      <c r="I34" s="63"/>
+      <c r="J34" s="65"/>
+    </row>
+    <row r="35" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C35" s="65" t="s">
+        <v>116</v>
+      </c>
+      <c r="D35" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E35" s="63" t="s">
+        <v>249</v>
+      </c>
+      <c r="F35" s="63"/>
+      <c r="G35" s="63"/>
+      <c r="H35" s="65" t="s">
+        <v>503</v>
+      </c>
+      <c r="I35" s="64" t="s">
+        <v>504</v>
+      </c>
+      <c r="J35" s="68" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="63"/>
+      <c r="F36" s="63"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="63"/>
+      <c r="J36" s="65"/>
+    </row>
+    <row r="37" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C37" s="66" t="s">
+        <v>506</v>
+      </c>
+      <c r="D37" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E37" s="63" t="s">
+        <v>511</v>
+      </c>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="65" t="s">
+        <v>512</v>
+      </c>
+      <c r="I37" s="64" t="s">
+        <v>513</v>
+      </c>
+      <c r="J37" s="65" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C38" s="67"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="63"/>
+      <c r="G38" s="63"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="65"/>
+    </row>
+    <row r="39" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C39" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E39" s="63" t="s">
+        <v>507</v>
+      </c>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="65" t="s">
+        <v>508</v>
+      </c>
+      <c r="I39" s="63" t="s">
+        <v>509</v>
+      </c>
+      <c r="J39" s="65" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C40" s="65"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="63"/>
+      <c r="G40" s="63"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="63"/>
+      <c r="J40" s="65"/>
+    </row>
+    <row r="41" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C41" s="65" t="s">
+        <v>515</v>
+      </c>
+      <c r="D41" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E41" s="63" t="s">
+        <v>516</v>
+      </c>
+      <c r="F41" s="63"/>
+      <c r="G41" s="63"/>
+      <c r="H41" s="65" t="s">
+        <v>517</v>
+      </c>
+      <c r="I41" s="64" t="s">
+        <v>518</v>
+      </c>
+      <c r="J41" s="65" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="42" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C42" s="65"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="63"/>
+      <c r="G42" s="63"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="63"/>
+      <c r="J42" s="65"/>
+    </row>
+    <row r="43" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C43" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="65" t="s">
+        <v>448</v>
+      </c>
+      <c r="E43" s="64" t="s">
+        <v>520</v>
+      </c>
+      <c r="F43" s="63"/>
+      <c r="G43" s="63"/>
+      <c r="H43" s="65" t="s">
+        <v>522</v>
+      </c>
+      <c r="I43" s="63" t="s">
+        <v>521</v>
+      </c>
+      <c r="J43" s="65" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="44" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C44" s="65"/>
+      <c r="D44" s="65"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="65"/>
+      <c r="I44" s="63"/>
+      <c r="J44" s="65"/>
+    </row>
+    <row r="45" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C45" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="D45" s="65" t="s">
+        <v>449</v>
+      </c>
+      <c r="E45" s="63" t="s">
+        <v>523</v>
+      </c>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="65" t="s">
+        <v>524</v>
+      </c>
+      <c r="I45" s="63"/>
+      <c r="J45" s="65"/>
+    </row>
+    <row r="46" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="C46" s="65"/>
+      <c r="D46" s="65"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="65"/>
+      <c r="I46" s="63"/>
+      <c r="J46" s="65"/>
+    </row>
+  </sheetData>
+  <mergeCells count="122">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="K8:K10"/>
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="E17:G18"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="J11:J13"/>
+    <mergeCell ref="E11:G13"/>
+    <mergeCell ref="E8:G10"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:G24"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="E19:G20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="J23:J24"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:G22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="J21:J22"/>
+    <mergeCell ref="J27:J28"/>
+    <mergeCell ref="K27:K28"/>
+    <mergeCell ref="B8:B28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="E27:G28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="K21:K22"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="E33:G34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="E31:G32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="E37:G38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="E35:G36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="E39:G40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="E45:G46"/>
+    <mergeCell ref="E43:G44"/>
+    <mergeCell ref="E41:G42"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="D41:D42"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
